--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,12 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527471.7370227635</v>
+        <v>527472</v>
       </c>
       <c r="R4" t="n">
-        <v>6326186.438260145</v>
+        <v>6326186</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1010,19 +1005,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -940,7 +940,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98563</v>
+        <v>98573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28468-2023 artfynd.xlsx
+++ b/artfynd/A 28468-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2482729</v>
+        <v>2477029</v>
       </c>
       <c r="B2" t="n">
-        <v>96272</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527379.8073653262</v>
+        <v>527380</v>
       </c>
       <c r="R2" t="n">
-        <v>6326335.287827692</v>
+        <v>6326335</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-07-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,12 +794,7 @@
         <v>2453683</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527379.8073653262</v>
+        <v>527380</v>
       </c>
       <c r="R3" t="n">
-        <v>6326335.287827692</v>
+        <v>6326335</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -893,19 +873,9 @@
           <t>2001-06-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2001-06-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,7 +910,7 @@
         <v>74129609</v>
       </c>
       <c r="B4" t="n">
-        <v>98573</v>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
